--- a/artfynd/A 38157-2023 artfynd.xlsx
+++ b/artfynd/A 38157-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -799,6 +799,1714 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121585700</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57356</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>691060</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7138192</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121585763</v>
+      </c>
+      <c r="B4" t="n">
+        <v>78609</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>691074</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7138194</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121585708</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90738</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>691151</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7138209</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121585745</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91439</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1105</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Laxporing</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Rhodonia placenta</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>691117</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7138198</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121585709</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58069</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>691167</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7138174</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121585728</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90685</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>691070</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7138139</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121585697</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>691096</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7138190</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121585936</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90685</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>691087</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7138101</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121585734</v>
+      </c>
+      <c r="B11" t="n">
+        <v>90738</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>691108</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7138192</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:58</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121585777</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58069</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103056</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Videsparv</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Emberiza rustica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>691100</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7138149</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121585739</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57372</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>691118</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7138202</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>121585736</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57509</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>691089</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7138171</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-08-28</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>121585917</v>
+      </c>
+      <c r="B15" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>691088</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7138098</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>121585748</v>
+      </c>
+      <c r="B16" t="n">
+        <v>90738</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långsele, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>691105</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7138177</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lycksele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-26</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:12</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Aron Dynesius</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38157-2023 artfynd.xlsx
+++ b/artfynd/A 38157-2023 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121585700</v>
+        <v>121585936</v>
       </c>
       <c r="B3" t="n">
-        <v>57356</v>
+        <v>90685</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,57 +814,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691060</v>
+        <v>691087</v>
       </c>
       <c r="R3" t="n">
-        <v>7138192</v>
+        <v>7138101</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -891,22 +872,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,10 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121585763</v>
+        <v>121585708</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -953,21 +934,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -977,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691074</v>
+        <v>691151</v>
       </c>
       <c r="R4" t="n">
-        <v>7138194</v>
+        <v>7138209</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1007,22 +988,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585708</v>
+        <v>121585697</v>
       </c>
       <c r="B5" t="n">
-        <v>90738</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,34 +1050,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691151</v>
+        <v>691096</v>
       </c>
       <c r="R5" t="n">
-        <v>7138209</v>
+        <v>7138190</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1128,7 +1123,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1138,7 +1133,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1169,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585745</v>
+        <v>121585763</v>
       </c>
       <c r="B6" t="n">
-        <v>91439</v>
+        <v>78609</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,25 +1176,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1105</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1209,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691117</v>
+        <v>691074</v>
       </c>
       <c r="R6" t="n">
-        <v>7138198</v>
+        <v>7138194</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1285,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585709</v>
+        <v>121585917</v>
       </c>
       <c r="B7" t="n">
-        <v>58069</v>
+        <v>90720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,48 +1296,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103056</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691167</v>
+        <v>691088</v>
       </c>
       <c r="R7" t="n">
-        <v>7138174</v>
+        <v>7138098</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1369,22 +1350,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1415,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585728</v>
+        <v>121585736</v>
       </c>
       <c r="B8" t="n">
-        <v>90685</v>
+        <v>57509</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1427,38 +1408,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691070</v>
+        <v>691089</v>
       </c>
       <c r="R8" t="n">
-        <v>7138139</v>
+        <v>7138171</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1485,22 +1480,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,10 +1526,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121585697</v>
+        <v>121585700</v>
       </c>
       <c r="B9" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1547,16 +1542,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1574,9 +1569,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1585,10 +1585,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691096</v>
+        <v>691060</v>
       </c>
       <c r="R9" t="n">
-        <v>7138190</v>
+        <v>7138192</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1661,10 +1661,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121585936</v>
+        <v>121585739</v>
       </c>
       <c r="B10" t="n">
-        <v>90685</v>
+        <v>57372</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1673,38 +1673,47 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691087</v>
+        <v>691118</v>
       </c>
       <c r="R10" t="n">
-        <v>7138101</v>
+        <v>7138202</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1731,22 +1740,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1777,10 +1786,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121585734</v>
+        <v>121585745</v>
       </c>
       <c r="B11" t="n">
-        <v>90738</v>
+        <v>91439</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1789,25 +1798,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>1105</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1817,10 +1826,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691108</v>
+        <v>691117</v>
       </c>
       <c r="R11" t="n">
-        <v>7138192</v>
+        <v>7138198</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1847,22 +1856,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2023,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585739</v>
+        <v>121585728</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>90685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2035,47 +2044,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691118</v>
+        <v>691070</v>
       </c>
       <c r="R13" t="n">
-        <v>7138202</v>
+        <v>7138139</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2102,22 +2102,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2148,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585736</v>
+        <v>121585709</v>
       </c>
       <c r="B14" t="n">
-        <v>57509</v>
+        <v>58069</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2164,26 +2164,26 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>103056</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pallas, 1776</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -2193,7 +2193,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2202,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691089</v>
+        <v>691167</v>
       </c>
       <c r="R14" t="n">
-        <v>7138171</v>
+        <v>7138174</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121585917</v>
+        <v>121585734</v>
       </c>
       <c r="B15" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2294,21 +2294,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2318,10 +2318,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691088</v>
+        <v>691108</v>
       </c>
       <c r="R15" t="n">
-        <v>7138098</v>
+        <v>7138192</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2348,22 +2348,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 38157-2023 artfynd.xlsx
+++ b/artfynd/A 38157-2023 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121585936</v>
+        <v>121585708</v>
       </c>
       <c r="B3" t="n">
-        <v>90685</v>
+        <v>90738</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,25 +814,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691087</v>
+        <v>691151</v>
       </c>
       <c r="R3" t="n">
-        <v>7138101</v>
+        <v>7138209</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,22 +872,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,7 +918,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121585708</v>
+        <v>121585748</v>
       </c>
       <c r="B4" t="n">
         <v>90738</v>
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691151</v>
+        <v>691105</v>
       </c>
       <c r="R4" t="n">
-        <v>7138209</v>
+        <v>7138177</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,22 +988,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585697</v>
+        <v>121585917</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1050,48 +1050,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691096</v>
+        <v>691088</v>
       </c>
       <c r="R5" t="n">
-        <v>7138190</v>
+        <v>7138098</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1118,22 +1104,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1164,10 +1150,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585763</v>
+        <v>121585700</v>
       </c>
       <c r="B6" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,34 +1166,53 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691074</v>
+        <v>691060</v>
       </c>
       <c r="R6" t="n">
-        <v>7138194</v>
+        <v>7138192</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1234,22 +1239,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585917</v>
+        <v>121585763</v>
       </c>
       <c r="B7" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,21 +1301,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1325,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691088</v>
+        <v>691074</v>
       </c>
       <c r="R7" t="n">
-        <v>7138098</v>
+        <v>7138194</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1526,10 +1531,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121585700</v>
+        <v>121585936</v>
       </c>
       <c r="B9" t="n">
-        <v>57356</v>
+        <v>90685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,57 +1543,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691060</v>
+        <v>691087</v>
       </c>
       <c r="R9" t="n">
-        <v>7138192</v>
+        <v>7138101</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1615,22 +1601,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1786,10 +1772,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121585745</v>
+        <v>121585709</v>
       </c>
       <c r="B11" t="n">
-        <v>91439</v>
+        <v>58069</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1798,38 +1784,52 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1105</v>
+        <v>103056</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691117</v>
+        <v>691167</v>
       </c>
       <c r="R11" t="n">
-        <v>7138198</v>
+        <v>7138174</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1856,22 +1856,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585777</v>
+        <v>121585734</v>
       </c>
       <c r="B12" t="n">
-        <v>58069</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1918,48 +1918,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103056</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691100</v>
+        <v>691108</v>
       </c>
       <c r="R12" t="n">
-        <v>7138149</v>
+        <v>7138192</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1991,7 +1977,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2001,7 +1987,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2032,10 +2018,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585728</v>
+        <v>121585777</v>
       </c>
       <c r="B13" t="n">
-        <v>90685</v>
+        <v>58069</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2044,38 +2030,52 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>103056</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691070</v>
+        <v>691100</v>
       </c>
       <c r="R13" t="n">
-        <v>7138139</v>
+        <v>7138149</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2102,22 +2102,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2148,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585709</v>
+        <v>121585728</v>
       </c>
       <c r="B14" t="n">
-        <v>58069</v>
+        <v>90685</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,52 +2160,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103056</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691167</v>
+        <v>691070</v>
       </c>
       <c r="R14" t="n">
-        <v>7138174</v>
+        <v>7138139</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2232,22 +2218,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2278,10 +2264,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121585734</v>
+        <v>121585745</v>
       </c>
       <c r="B15" t="n">
-        <v>90738</v>
+        <v>91439</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2290,25 +2276,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1105</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2318,10 +2304,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691108</v>
+        <v>691117</v>
       </c>
       <c r="R15" t="n">
-        <v>7138192</v>
+        <v>7138198</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2348,22 +2334,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2394,10 +2380,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585748</v>
+        <v>121585697</v>
       </c>
       <c r="B16" t="n">
-        <v>90738</v>
+        <v>57372</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2410,34 +2396,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691105</v>
+        <v>691096</v>
       </c>
       <c r="R16" t="n">
-        <v>7138177</v>
+        <v>7138190</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2464,22 +2464,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 38157-2023 artfynd.xlsx
+++ b/artfynd/A 38157-2023 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121585708</v>
+        <v>121585736</v>
       </c>
       <c r="B3" t="n">
-        <v>90738</v>
+        <v>57509</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,34 +818,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691151</v>
+        <v>691089</v>
       </c>
       <c r="R3" t="n">
-        <v>7138209</v>
+        <v>7138171</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,7 +891,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -887,7 +901,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121585748</v>
+        <v>121585728</v>
       </c>
       <c r="B4" t="n">
-        <v>90738</v>
+        <v>90685</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -930,25 +944,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -958,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691105</v>
+        <v>691070</v>
       </c>
       <c r="R4" t="n">
-        <v>7138177</v>
+        <v>7138139</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1034,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585917</v>
+        <v>121585745</v>
       </c>
       <c r="B5" t="n">
-        <v>90720</v>
+        <v>91439</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,25 +1060,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1105</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1074,10 +1088,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691088</v>
+        <v>691117</v>
       </c>
       <c r="R5" t="n">
-        <v>7138098</v>
+        <v>7138198</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1150,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585700</v>
+        <v>121585936</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>90685</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1162,57 +1176,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691060</v>
+        <v>691087</v>
       </c>
       <c r="R6" t="n">
-        <v>7138192</v>
+        <v>7138101</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1239,22 +1234,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585763</v>
+        <v>121585777</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>58069</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,34 +1296,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>103056</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691074</v>
+        <v>691100</v>
       </c>
       <c r="R7" t="n">
-        <v>7138194</v>
+        <v>7138149</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,22 +1364,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1401,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585736</v>
+        <v>121585708</v>
       </c>
       <c r="B8" t="n">
-        <v>57509</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,48 +1426,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691089</v>
+        <v>691151</v>
       </c>
       <c r="R8" t="n">
-        <v>7138171</v>
+        <v>7138209</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1490,7 +1485,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1500,7 +1495,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1531,10 +1526,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121585936</v>
+        <v>121585734</v>
       </c>
       <c r="B9" t="n">
-        <v>90685</v>
+        <v>90738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1543,25 +1538,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1571,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691087</v>
+        <v>691108</v>
       </c>
       <c r="R9" t="n">
-        <v>7138101</v>
+        <v>7138192</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1601,22 +1596,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1772,10 +1767,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121585709</v>
+        <v>121585748</v>
       </c>
       <c r="B11" t="n">
-        <v>58069</v>
+        <v>90738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1788,48 +1783,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103056</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691167</v>
+        <v>691105</v>
       </c>
       <c r="R11" t="n">
-        <v>7138174</v>
+        <v>7138177</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1856,22 +1837,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,10 +1883,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585734</v>
+        <v>121585700</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1918,31 +1899,50 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691108</v>
+        <v>691060</v>
       </c>
       <c r="R12" t="n">
         <v>7138192</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2018,7 +2018,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585777</v>
+        <v>121585709</v>
       </c>
       <c r="B13" t="n">
         <v>58069</v>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691100</v>
+        <v>691167</v>
       </c>
       <c r="R13" t="n">
-        <v>7138149</v>
+        <v>7138174</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585728</v>
+        <v>121585697</v>
       </c>
       <c r="B14" t="n">
-        <v>90685</v>
+        <v>57372</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2160,38 +2160,52 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691070</v>
+        <v>691096</v>
       </c>
       <c r="R14" t="n">
-        <v>7138139</v>
+        <v>7138190</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2218,22 +2232,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2264,10 +2278,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121585745</v>
+        <v>121585763</v>
       </c>
       <c r="B15" t="n">
-        <v>91439</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2276,25 +2290,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1105</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2304,10 +2318,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691117</v>
+        <v>691074</v>
       </c>
       <c r="R15" t="n">
-        <v>7138198</v>
+        <v>7138194</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2380,10 +2394,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585697</v>
+        <v>121585917</v>
       </c>
       <c r="B16" t="n">
-        <v>57372</v>
+        <v>90720</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2396,48 +2410,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691096</v>
+        <v>691088</v>
       </c>
       <c r="R16" t="n">
-        <v>7138190</v>
+        <v>7138098</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2464,22 +2464,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 38157-2023 artfynd.xlsx
+++ b/artfynd/A 38157-2023 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121585736</v>
+        <v>121585739</v>
       </c>
       <c r="B3" t="n">
-        <v>57509</v>
+        <v>57372</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,36 +818,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -856,10 +851,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691089</v>
+        <v>691118</v>
       </c>
       <c r="R3" t="n">
-        <v>7138171</v>
+        <v>7138202</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -932,10 +927,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121585728</v>
+        <v>121585745</v>
       </c>
       <c r="B4" t="n">
-        <v>90685</v>
+        <v>91439</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,25 +939,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1105</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -972,10 +967,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691070</v>
+        <v>691117</v>
       </c>
       <c r="R4" t="n">
-        <v>7138139</v>
+        <v>7138198</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1048,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585745</v>
+        <v>121585763</v>
       </c>
       <c r="B5" t="n">
-        <v>91439</v>
+        <v>78609</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1060,25 +1055,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1105</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1088,10 +1083,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691117</v>
+        <v>691074</v>
       </c>
       <c r="R5" t="n">
-        <v>7138198</v>
+        <v>7138194</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1164,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585936</v>
+        <v>121585700</v>
       </c>
       <c r="B6" t="n">
-        <v>90685</v>
+        <v>57356</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1176,38 +1171,57 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691087</v>
+        <v>691060</v>
       </c>
       <c r="R6" t="n">
-        <v>7138101</v>
+        <v>7138192</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1234,22 +1248,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1294,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585777</v>
+        <v>121585917</v>
       </c>
       <c r="B7" t="n">
-        <v>58069</v>
+        <v>90720</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1296,48 +1310,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103056</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691100</v>
+        <v>691088</v>
       </c>
       <c r="R7" t="n">
-        <v>7138149</v>
+        <v>7138098</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1364,22 +1364,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585708</v>
+        <v>121585936</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>90685</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,25 +1422,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691151</v>
+        <v>691087</v>
       </c>
       <c r="R8" t="n">
-        <v>7138209</v>
+        <v>7138101</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1480,22 +1480,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1642,10 +1642,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121585739</v>
+        <v>121585777</v>
       </c>
       <c r="B10" t="n">
-        <v>57372</v>
+        <v>58069</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,31 +1658,36 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>103056</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pallas, 1776</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1691,10 +1696,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691118</v>
+        <v>691100</v>
       </c>
       <c r="R10" t="n">
-        <v>7138202</v>
+        <v>7138149</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1767,10 +1772,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121585748</v>
+        <v>121585697</v>
       </c>
       <c r="B11" t="n">
-        <v>90738</v>
+        <v>57372</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1783,34 +1788,48 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691105</v>
+        <v>691096</v>
       </c>
       <c r="R11" t="n">
-        <v>7138177</v>
+        <v>7138190</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1837,22 +1856,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1883,10 +1902,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585700</v>
+        <v>121585708</v>
       </c>
       <c r="B12" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1899,53 +1918,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691060</v>
+        <v>691151</v>
       </c>
       <c r="R12" t="n">
-        <v>7138192</v>
+        <v>7138209</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1977,7 +1977,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2018,10 +2018,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585709</v>
+        <v>121585728</v>
       </c>
       <c r="B13" t="n">
-        <v>58069</v>
+        <v>90685</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2030,52 +2030,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103056</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691167</v>
+        <v>691070</v>
       </c>
       <c r="R13" t="n">
-        <v>7138174</v>
+        <v>7138139</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2102,22 +2088,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2148,10 +2134,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585697</v>
+        <v>121585736</v>
       </c>
       <c r="B14" t="n">
-        <v>57372</v>
+        <v>57509</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2164,21 +2150,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2202,10 +2188,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691096</v>
+        <v>691089</v>
       </c>
       <c r="R14" t="n">
-        <v>7138190</v>
+        <v>7138171</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2278,10 +2264,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121585763</v>
+        <v>121585709</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>58069</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2294,34 +2280,48 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>103056</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691074</v>
+        <v>691167</v>
       </c>
       <c r="R15" t="n">
-        <v>7138194</v>
+        <v>7138174</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2348,22 +2348,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2394,10 +2394,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585917</v>
+        <v>121585748</v>
       </c>
       <c r="B16" t="n">
-        <v>90720</v>
+        <v>90738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2410,21 +2410,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691088</v>
+        <v>691105</v>
       </c>
       <c r="R16" t="n">
-        <v>7138098</v>
+        <v>7138177</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 38157-2023 artfynd.xlsx
+++ b/artfynd/A 38157-2023 artfynd.xlsx
@@ -1410,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585936</v>
+        <v>121585734</v>
       </c>
       <c r="B8" t="n">
-        <v>90685</v>
+        <v>90738</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,25 +1422,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691087</v>
+        <v>691108</v>
       </c>
       <c r="R8" t="n">
-        <v>7138101</v>
+        <v>7138192</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1480,22 +1480,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121585734</v>
+        <v>121585936</v>
       </c>
       <c r="B9" t="n">
-        <v>90738</v>
+        <v>90685</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,25 +1538,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691108</v>
+        <v>691087</v>
       </c>
       <c r="R9" t="n">
-        <v>7138192</v>
+        <v>7138101</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1596,22 +1596,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 38157-2023 artfynd.xlsx
+++ b/artfynd/A 38157-2023 artfynd.xlsx
@@ -1410,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585734</v>
+        <v>121585936</v>
       </c>
       <c r="B8" t="n">
-        <v>90738</v>
+        <v>90685</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,25 +1422,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691108</v>
+        <v>691087</v>
       </c>
       <c r="R8" t="n">
-        <v>7138192</v>
+        <v>7138101</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1480,22 +1480,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121585936</v>
+        <v>121585734</v>
       </c>
       <c r="B9" t="n">
-        <v>90685</v>
+        <v>90738</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1538,25 +1538,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1566,10 +1566,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691087</v>
+        <v>691108</v>
       </c>
       <c r="R9" t="n">
-        <v>7138101</v>
+        <v>7138192</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1596,22 +1596,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1902,10 +1902,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585708</v>
+        <v>121585728</v>
       </c>
       <c r="B12" t="n">
-        <v>90738</v>
+        <v>90685</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1914,25 +1914,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691151</v>
+        <v>691070</v>
       </c>
       <c r="R12" t="n">
-        <v>7138209</v>
+        <v>7138139</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1972,22 +1972,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2018,10 +2018,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585728</v>
+        <v>121585708</v>
       </c>
       <c r="B13" t="n">
-        <v>90685</v>
+        <v>90738</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2030,25 +2030,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2058,10 +2058,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691070</v>
+        <v>691151</v>
       </c>
       <c r="R13" t="n">
-        <v>7138139</v>
+        <v>7138209</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2088,22 +2088,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 38157-2023 artfynd.xlsx
+++ b/artfynd/A 38157-2023 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121585739</v>
+        <v>121585736</v>
       </c>
       <c r="B3" t="n">
-        <v>57372</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,31 +818,36 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -851,10 +856,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691118</v>
+        <v>691089</v>
       </c>
       <c r="R3" t="n">
-        <v>7138202</v>
+        <v>7138171</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -927,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121585745</v>
+        <v>121585728</v>
       </c>
       <c r="B4" t="n">
-        <v>91439</v>
+        <v>90693</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -939,25 +944,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1105</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -967,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691117</v>
+        <v>691070</v>
       </c>
       <c r="R4" t="n">
-        <v>7138198</v>
+        <v>7138139</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1046,7 +1051,7 @@
         <v>121585763</v>
       </c>
       <c r="B5" t="n">
-        <v>78609</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1159,10 +1164,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585700</v>
+        <v>121585708</v>
       </c>
       <c r="B6" t="n">
-        <v>57356</v>
+        <v>90746</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,53 +1180,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691060</v>
+        <v>691151</v>
       </c>
       <c r="R6" t="n">
-        <v>7138192</v>
+        <v>7138209</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1253,7 +1239,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1263,7 +1249,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585917</v>
+        <v>121585748</v>
       </c>
       <c r="B7" t="n">
-        <v>90720</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,21 +1296,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1334,10 +1320,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691088</v>
+        <v>691105</v>
       </c>
       <c r="R7" t="n">
-        <v>7138098</v>
+        <v>7138177</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1410,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585936</v>
+        <v>121585777</v>
       </c>
       <c r="B8" t="n">
-        <v>90685</v>
+        <v>58070</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1422,38 +1408,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>103056</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691087</v>
+        <v>691100</v>
       </c>
       <c r="R8" t="n">
-        <v>7138101</v>
+        <v>7138149</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1480,22 +1480,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1526,10 +1526,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121585734</v>
+        <v>121585697</v>
       </c>
       <c r="B9" t="n">
-        <v>90738</v>
+        <v>57373</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1542,34 +1542,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691108</v>
+        <v>691096</v>
       </c>
       <c r="R9" t="n">
-        <v>7138192</v>
+        <v>7138190</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1601,7 +1615,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1611,7 +1625,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1642,10 +1656,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121585777</v>
+        <v>121585700</v>
       </c>
       <c r="B10" t="n">
-        <v>58069</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1658,26 +1672,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103056</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1685,9 +1699,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1696,10 +1715,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691100</v>
+        <v>691060</v>
       </c>
       <c r="R10" t="n">
-        <v>7138149</v>
+        <v>7138192</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1772,10 +1791,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121585697</v>
+        <v>121585739</v>
       </c>
       <c r="B11" t="n">
-        <v>57372</v>
+        <v>57373</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1807,17 +1826,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
+          <t>3</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1826,10 +1840,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691096</v>
+        <v>691118</v>
       </c>
       <c r="R11" t="n">
-        <v>7138190</v>
+        <v>7138202</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1902,10 +1916,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585728</v>
+        <v>121585734</v>
       </c>
       <c r="B12" t="n">
-        <v>90685</v>
+        <v>90746</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1914,25 +1928,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1942,10 +1956,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691070</v>
+        <v>691108</v>
       </c>
       <c r="R12" t="n">
-        <v>7138139</v>
+        <v>7138192</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1972,22 +1986,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2018,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585708</v>
+        <v>121585745</v>
       </c>
       <c r="B13" t="n">
-        <v>90738</v>
+        <v>91447</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2030,25 +2044,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1105</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2058,10 +2072,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691151</v>
+        <v>691117</v>
       </c>
       <c r="R13" t="n">
-        <v>7138209</v>
+        <v>7138198</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2088,22 +2102,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2134,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585736</v>
+        <v>121585917</v>
       </c>
       <c r="B14" t="n">
-        <v>57509</v>
+        <v>90728</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2150,48 +2164,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691089</v>
+        <v>691088</v>
       </c>
       <c r="R14" t="n">
-        <v>7138171</v>
+        <v>7138098</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2218,22 +2218,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2267,7 +2267,7 @@
         <v>121585709</v>
       </c>
       <c r="B15" t="n">
-        <v>58069</v>
+        <v>58070</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585748</v>
+        <v>121585936</v>
       </c>
       <c r="B16" t="n">
-        <v>90738</v>
+        <v>90693</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2406,25 +2406,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2434,10 +2434,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691105</v>
+        <v>691087</v>
       </c>
       <c r="R16" t="n">
-        <v>7138177</v>
+        <v>7138101</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>

--- a/artfynd/A 38157-2023 artfynd.xlsx
+++ b/artfynd/A 38157-2023 artfynd.xlsx
@@ -1916,10 +1916,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585734</v>
+        <v>121585745</v>
       </c>
       <c r="B12" t="n">
-        <v>90746</v>
+        <v>91447</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1928,25 +1928,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>1105</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1956,10 +1956,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691108</v>
+        <v>691117</v>
       </c>
       <c r="R12" t="n">
-        <v>7138192</v>
+        <v>7138198</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1986,22 +1986,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585745</v>
+        <v>121585917</v>
       </c>
       <c r="B13" t="n">
-        <v>91447</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2044,25 +2044,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1105</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691117</v>
+        <v>691088</v>
       </c>
       <c r="R13" t="n">
-        <v>7138198</v>
+        <v>7138098</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2148,10 +2148,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585917</v>
+        <v>121585734</v>
       </c>
       <c r="B14" t="n">
-        <v>90728</v>
+        <v>90746</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2164,21 +2164,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2188,10 +2188,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691088</v>
+        <v>691108</v>
       </c>
       <c r="R14" t="n">
-        <v>7138098</v>
+        <v>7138192</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2218,22 +2218,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 38157-2023 artfynd.xlsx
+++ b/artfynd/A 38157-2023 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121585763</v>
+        <v>121585736</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>57510</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,34 +818,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691074</v>
+        <v>691089</v>
       </c>
       <c r="R3" t="n">
-        <v>7138194</v>
+        <v>7138171</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,22 +886,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,10 +932,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121585736</v>
+        <v>121585777</v>
       </c>
       <c r="B4" t="n">
-        <v>57510</v>
+        <v>58070</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,26 +948,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>103056</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pallas, 1776</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -963,7 +977,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -972,10 +986,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691089</v>
+        <v>691100</v>
       </c>
       <c r="R4" t="n">
-        <v>7138171</v>
+        <v>7138149</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1048,10 +1062,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585748</v>
+        <v>121585763</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,21 +1078,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1088,10 +1102,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691105</v>
+        <v>691074</v>
       </c>
       <c r="R5" t="n">
-        <v>7138177</v>
+        <v>7138194</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1164,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585917</v>
+        <v>121585748</v>
       </c>
       <c r="B6" t="n">
-        <v>90728</v>
+        <v>90746</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1180,21 +1194,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1204,10 +1218,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691088</v>
+        <v>691105</v>
       </c>
       <c r="R6" t="n">
-        <v>7138098</v>
+        <v>7138177</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1280,10 +1294,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585936</v>
+        <v>121585734</v>
       </c>
       <c r="B7" t="n">
-        <v>90693</v>
+        <v>90746</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,25 +1306,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1320,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691087</v>
+        <v>691108</v>
       </c>
       <c r="R7" t="n">
-        <v>7138101</v>
+        <v>7138192</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1350,22 +1364,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1396,10 +1410,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585745</v>
+        <v>121585709</v>
       </c>
       <c r="B8" t="n">
-        <v>91447</v>
+        <v>58070</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1408,38 +1422,52 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1105</v>
+        <v>103056</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691117</v>
+        <v>691167</v>
       </c>
       <c r="R8" t="n">
-        <v>7138198</v>
+        <v>7138174</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1466,22 +1494,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121585700</v>
+        <v>121585936</v>
       </c>
       <c r="B9" t="n">
-        <v>57357</v>
+        <v>90693</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1524,57 +1552,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691060</v>
+        <v>691087</v>
       </c>
       <c r="R9" t="n">
-        <v>7138192</v>
+        <v>7138101</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1601,22 +1610,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,10 +1656,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121585739</v>
+        <v>121585700</v>
       </c>
       <c r="B10" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1663,16 +1672,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1682,12 +1691,22 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1696,10 +1715,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691118</v>
+        <v>691060</v>
       </c>
       <c r="R10" t="n">
-        <v>7138202</v>
+        <v>7138192</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1772,10 +1791,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121585709</v>
+        <v>121585728</v>
       </c>
       <c r="B11" t="n">
-        <v>58070</v>
+        <v>90693</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1784,52 +1803,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103056</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691167</v>
+        <v>691070</v>
       </c>
       <c r="R11" t="n">
-        <v>7138174</v>
+        <v>7138139</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1856,22 +1861,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1902,10 +1907,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585697</v>
+        <v>121585708</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>90746</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1918,48 +1923,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691096</v>
+        <v>691151</v>
       </c>
       <c r="R12" t="n">
-        <v>7138190</v>
+        <v>7138209</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1991,7 +1982,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2001,7 +1992,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2032,10 +2023,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585777</v>
+        <v>121585917</v>
       </c>
       <c r="B13" t="n">
-        <v>58070</v>
+        <v>90728</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2048,48 +2039,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103056</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691100</v>
+        <v>691088</v>
       </c>
       <c r="R13" t="n">
-        <v>7138149</v>
+        <v>7138098</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2116,22 +2093,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2162,10 +2139,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585734</v>
+        <v>121585739</v>
       </c>
       <c r="B14" t="n">
-        <v>90746</v>
+        <v>57373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2178,34 +2155,43 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691108</v>
+        <v>691118</v>
       </c>
       <c r="R14" t="n">
-        <v>7138192</v>
+        <v>7138202</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2237,7 +2223,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2247,7 +2233,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2278,10 +2264,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121585728</v>
+        <v>121585745</v>
       </c>
       <c r="B15" t="n">
-        <v>90693</v>
+        <v>91447</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2290,25 +2276,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>1105</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2318,10 +2304,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691070</v>
+        <v>691117</v>
       </c>
       <c r="R15" t="n">
-        <v>7138139</v>
+        <v>7138198</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2394,10 +2380,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585708</v>
+        <v>121585697</v>
       </c>
       <c r="B16" t="n">
-        <v>90746</v>
+        <v>57373</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2410,34 +2396,48 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691151</v>
+        <v>691096</v>
       </c>
       <c r="R16" t="n">
-        <v>7138209</v>
+        <v>7138190</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 38157-2023 artfynd.xlsx
+++ b/artfynd/A 38157-2023 artfynd.xlsx
@@ -1178,7 +1178,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585748</v>
+        <v>121585734</v>
       </c>
       <c r="B6" t="n">
         <v>90746</v>
@@ -1218,10 +1218,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691105</v>
+        <v>691108</v>
       </c>
       <c r="R6" t="n">
-        <v>7138177</v>
+        <v>7138192</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1248,22 +1248,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,7 +1294,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585734</v>
+        <v>121585748</v>
       </c>
       <c r="B7" t="n">
         <v>90746</v>
@@ -1334,10 +1334,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691108</v>
+        <v>691105</v>
       </c>
       <c r="R7" t="n">
-        <v>7138192</v>
+        <v>7138177</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1364,22 +1364,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 38157-2023 artfynd.xlsx
+++ b/artfynd/A 38157-2023 artfynd.xlsx
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121585736</v>
+        <v>121585917</v>
       </c>
       <c r="B3" t="n">
-        <v>57510</v>
+        <v>90728</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,48 +818,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691089</v>
+        <v>691088</v>
       </c>
       <c r="R3" t="n">
-        <v>7138171</v>
+        <v>7138098</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -886,22 +872,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1062,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585763</v>
+        <v>121585700</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1078,34 +1064,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691074</v>
+        <v>691060</v>
       </c>
       <c r="R5" t="n">
-        <v>7138194</v>
+        <v>7138192</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1132,22 +1137,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,10 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585734</v>
+        <v>121585763</v>
       </c>
       <c r="B6" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,21 +1199,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1218,10 +1223,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691108</v>
+        <v>691074</v>
       </c>
       <c r="R6" t="n">
-        <v>7138192</v>
+        <v>7138194</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1248,22 +1253,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1294,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585748</v>
+        <v>121585739</v>
       </c>
       <c r="B7" t="n">
-        <v>90746</v>
+        <v>57373</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1310,34 +1315,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691105</v>
+        <v>691118</v>
       </c>
       <c r="R7" t="n">
-        <v>7138177</v>
+        <v>7138202</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1364,22 +1378,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1410,10 +1424,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585709</v>
+        <v>121585734</v>
       </c>
       <c r="B8" t="n">
-        <v>58070</v>
+        <v>90746</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1426,48 +1440,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103056</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691167</v>
+        <v>691108</v>
       </c>
       <c r="R8" t="n">
-        <v>7138174</v>
+        <v>7138192</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1540,10 +1540,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121585936</v>
+        <v>121585736</v>
       </c>
       <c r="B9" t="n">
-        <v>90693</v>
+        <v>57510</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1552,38 +1552,52 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691087</v>
+        <v>691089</v>
       </c>
       <c r="R9" t="n">
-        <v>7138101</v>
+        <v>7138171</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1610,22 +1624,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,10 +1670,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121585700</v>
+        <v>121585936</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>90693</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1668,57 +1682,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691060</v>
+        <v>691087</v>
       </c>
       <c r="R10" t="n">
-        <v>7138192</v>
+        <v>7138101</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1745,22 +1740,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1907,7 +1902,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585708</v>
+        <v>121585748</v>
       </c>
       <c r="B12" t="n">
         <v>90746</v>
@@ -1947,10 +1942,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691151</v>
+        <v>691105</v>
       </c>
       <c r="R12" t="n">
-        <v>7138209</v>
+        <v>7138177</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1977,22 +1972,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2023,10 +2018,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585917</v>
+        <v>121585709</v>
       </c>
       <c r="B13" t="n">
-        <v>90728</v>
+        <v>58070</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2039,34 +2034,48 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>103056</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691088</v>
+        <v>691167</v>
       </c>
       <c r="R13" t="n">
-        <v>7138098</v>
+        <v>7138174</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2093,22 +2102,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2139,7 +2148,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585739</v>
+        <v>121585697</v>
       </c>
       <c r="B14" t="n">
         <v>57373</v>
@@ -2174,12 +2183,17 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2188,10 +2202,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691118</v>
+        <v>691096</v>
       </c>
       <c r="R14" t="n">
-        <v>7138202</v>
+        <v>7138190</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2264,10 +2278,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121585745</v>
+        <v>121585708</v>
       </c>
       <c r="B15" t="n">
-        <v>91447</v>
+        <v>90746</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2276,25 +2290,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1105</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2304,10 +2318,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691117</v>
+        <v>691151</v>
       </c>
       <c r="R15" t="n">
-        <v>7138198</v>
+        <v>7138209</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2334,22 +2348,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2380,10 +2394,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585697</v>
+        <v>121585745</v>
       </c>
       <c r="B16" t="n">
-        <v>57373</v>
+        <v>91447</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2392,52 +2406,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>1105</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691096</v>
+        <v>691117</v>
       </c>
       <c r="R16" t="n">
-        <v>7138190</v>
+        <v>7138198</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2464,22 +2464,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 38157-2023 artfynd.xlsx
+++ b/artfynd/A 38157-2023 artfynd.xlsx
@@ -675,65 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119387420</v>
+        <v>121585745</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92662</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1105</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Blåsartjärnen, Ly lm</t>
+          <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691055</v>
+        <v>691117</v>
       </c>
       <c r="R2" t="n">
-        <v>7138166</v>
+        <v>7138198</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -760,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:13</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,19 +778,18 @@
           <t>Aron Dynesius</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121585700</v>
+        <v>121585917</v>
       </c>
       <c r="B3" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -818,53 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>691060</v>
+        <v>691088</v>
       </c>
       <c r="R3" t="n">
-        <v>7138192</v>
+        <v>7138098</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -891,22 +851,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -937,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121585763</v>
+        <v>121585933</v>
       </c>
       <c r="B4" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -977,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>691074</v>
+        <v>691014</v>
       </c>
       <c r="R4" t="n">
-        <v>7138194</v>
+        <v>7138088</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1053,64 +1008,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121585777</v>
+        <v>121585728</v>
       </c>
       <c r="B5" t="n">
-        <v>58078</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103056</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>691100</v>
+        <v>691070</v>
       </c>
       <c r="R5" t="n">
-        <v>7138149</v>
+        <v>7138139</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1137,22 +1073,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1183,59 +1119,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121585739</v>
+        <v>121585922</v>
       </c>
       <c r="B6" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>691118</v>
+        <v>691028</v>
       </c>
       <c r="R6" t="n">
-        <v>7138202</v>
+        <v>7138087</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1262,22 +1184,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1308,15 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121585728</v>
+        <v>121585936</v>
       </c>
       <c r="B7" t="n">
-        <v>90707</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>691070</v>
+        <v>691087</v>
       </c>
       <c r="R7" t="n">
-        <v>7138139</v>
+        <v>7138101</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1424,37 +1341,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121585708</v>
+        <v>121585754</v>
       </c>
       <c r="B8" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1464,10 +1376,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>691151</v>
+        <v>691045</v>
       </c>
       <c r="R8" t="n">
-        <v>7138209</v>
+        <v>7138087</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1494,22 +1406,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1540,37 +1452,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121585734</v>
+        <v>121585763</v>
       </c>
       <c r="B9" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1580,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>691108</v>
+        <v>691074</v>
       </c>
       <c r="R9" t="n">
-        <v>7138192</v>
+        <v>7138194</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1610,22 +1517,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-08-28</t>
+          <t>2024-08-26</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1656,15 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121585936</v>
+        <v>121585697</v>
       </c>
       <c r="B10" t="n">
-        <v>90707</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1672,34 +1574,48 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>691087</v>
+        <v>691096</v>
       </c>
       <c r="R10" t="n">
-        <v>7138101</v>
+        <v>7138190</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1726,22 +1642,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,50 +1688,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121585745</v>
+        <v>121585739</v>
       </c>
       <c r="B11" t="n">
-        <v>91461</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1105</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>691117</v>
+        <v>691118</v>
       </c>
       <c r="R11" t="n">
-        <v>7138198</v>
+        <v>7138202</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1842,22 +1762,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1888,15 +1808,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121585697</v>
+        <v>119387420</v>
       </c>
       <c r="B12" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1904,16 +1819,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1921,31 +1836,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>adult</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långsele, Ly lm</t>
+          <t>Blåsartjärnen, Ly lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>691096</v>
+        <v>691055</v>
       </c>
       <c r="R12" t="n">
-        <v>7138190</v>
+        <v>7138166</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1977,7 +1893,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1987,7 +1903,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2010,23 +1926,14 @@
           <t>Aron Dynesius</t>
         </is>
       </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121585709</v>
+        <v>121585700</v>
       </c>
       <c r="B13" t="n">
-        <v>58078</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2034,26 +1941,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103056</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Videsparv</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza rustica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Pallas, 1776</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -2061,9 +1968,14 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2072,10 +1984,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>691167</v>
+        <v>691060</v>
       </c>
       <c r="R13" t="n">
-        <v>7138174</v>
+        <v>7138192</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2148,15 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121585917</v>
+        <v>121585736</v>
       </c>
       <c r="B14" t="n">
-        <v>90742</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,34 +2071,48 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>691088</v>
+        <v>691089</v>
       </c>
       <c r="R14" t="n">
-        <v>7138098</v>
+        <v>7138171</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2218,22 +2139,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2264,42 +2185,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121585736</v>
+        <v>121585709</v>
       </c>
       <c r="B15" t="n">
-        <v>57518</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>103056</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Pallas, 1776</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2309,7 +2225,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2318,10 +2234,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>691089</v>
+        <v>691167</v>
       </c>
       <c r="R15" t="n">
-        <v>7138171</v>
+        <v>7138174</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2394,50 +2310,59 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121585748</v>
+        <v>121585777</v>
       </c>
       <c r="B16" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58656</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>103056</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Videsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Emberiza rustica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Pallas, 1776</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Långsele, Ly lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>691105</v>
+        <v>691100</v>
       </c>
       <c r="R16" t="n">
-        <v>7138177</v>
+        <v>7138149</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2464,22 +2389,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-08-26</t>
+          <t>2024-08-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 38157-2023 artfynd.xlsx
+++ b/artfynd/A 38157-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585745</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585917</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585933</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585728</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585922</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585936</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585754</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585763</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1685,6 +1730,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585697</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1805,6 +1855,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585739</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1927,6 +1982,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119387420</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2057,6 +2117,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585700</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2182,6 +2247,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585736</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2307,6 +2377,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585709</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2432,8 +2507,30 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121585777</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>